--- a/src/nodes/LPC/compressor_stage_3_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/LPC/compressor_stage_3_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>20.26908783120912</v>
+        <v>19.914497247723702</v>
       </c>
       <c r="B1">
-        <v>21.070200596477843</v>
+        <v>21.4056551886526</v>
       </c>
       <c r="C1">
         <v>338.16769933532214</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>18.518545814435996</v>
+        <v>18.170888910995163</v>
       </c>
       <c r="B2">
-        <v>20.669497881199398</v>
+        <v>20.975783130232454</v>
       </c>
       <c r="C2">
         <v>338.16769933532214</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>16.924209481785859</v>
+        <v>16.586641168933102</v>
       </c>
       <c r="B3">
-        <v>20.078517065027317</v>
+        <v>20.358267334108206</v>
       </c>
       <c r="C3">
         <v>338.16769933532214</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>15.364752841069279</v>
+        <v>15.037977589377816</v>
       </c>
       <c r="B4">
-        <v>19.445048412525008</v>
+        <v>19.698851937459661</v>
       </c>
       <c r="C4">
         <v>338.16769933532214</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>13.833286822252115</v>
+        <v>13.51786996267418</v>
       </c>
       <c r="B5">
-        <v>18.777483674417642</v>
+        <v>19.005812508860181</v>
       </c>
       <c r="C5">
         <v>338.16769933532214</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>12.326921971830359</v>
+        <v>12.02337047657551</v>
       </c>
       <c r="B6">
-        <v>18.079342567215225</v>
+        <v>18.282620035031268</v>
       </c>
       <c r="C6">
         <v>338.16769933532214</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>10.843960623734137</v>
+        <v>10.552747176985768</v>
       </c>
       <c r="B7">
-        <v>17.352693060963407</v>
+        <v>17.531313855376695</v>
       </c>
       <c r="C7">
         <v>338.16769933532214</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>9.3833573054730763</v>
+        <v>9.10493347584378</v>
       </c>
       <c r="B8">
-        <v>16.59880867218704</v>
+        <v>16.753149854833445</v>
       </c>
       <c r="C8">
         <v>338.16769933532214</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>7.9435612351247062</v>
+        <v>7.6783472698429316</v>
       </c>
       <c r="B9">
-        <v>15.819578447630892</v>
+        <v>15.949990926662602</v>
       </c>
       <c r="C9">
         <v>338.16769933532214</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>6.5229133984944108</v>
+        <v>6.2712960374203988</v>
       </c>
       <c r="B10">
-        <v>15.017023274512216</v>
+        <v>15.123829979292109</v>
       </c>
       <c r="C10">
         <v>338.16769933532214</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>5.1198271617310951</v>
+        <v>4.88216109923395</v>
       </c>
       <c r="B11">
-        <v>14.193075871718268</v>
+        <v>14.276572973493236</v>
       </c>
       <c r="C11">
         <v>338.16769933532214</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>3.7334188801897228</v>
+        <v>3.510040963529959</v>
       </c>
       <c r="B12">
-        <v>13.348812629175987</v>
+        <v>13.40928139678436</v>
       </c>
       <c r="C12">
         <v>338.16769933532214</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2.3655444857060361</v>
+        <v>2.1568290466886615</v>
       </c>
       <c r="B13">
-        <v>12.481972789301075</v>
+        <v>12.519725791328929</v>
       </c>
       <c r="C13">
         <v>338.16769933532214</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>1.0172900638480038</v>
+        <v>0.823633370117485</v>
       </c>
       <c r="B14">
-        <v>11.59123336375005</v>
+        <v>11.606601485299008</v>
       </c>
       <c r="C14">
         <v>338.16769933532214</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.316077261368234</v>
+        <v>-0.49437453280119437</v>
       </c>
       <c r="B15">
-        <v>10.682359588653902</v>
+        <v>10.675593896255965</v>
       </c>
       <c r="C15">
         <v>338.16769933532214</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.6388982039879643</v>
+        <v>-1.8016230461906382</v>
       </c>
       <c r="B16">
-        <v>9.7606389977518635</v>
+        <v>9.7319173530658514</v>
       </c>
       <c r="C16">
         <v>338.16769933532214</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.9481258687503775</v>
+        <v>-3.0950037361716647</v>
       </c>
       <c r="B17">
-        <v>8.8223600907416</v>
+        <v>8.77191174042402</v>
       </c>
       <c r="C17">
         <v>338.16769933532214</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.2398067288902821</v>
+        <v>-4.3704832259829356</v>
       </c>
       <c r="B18">
-        <v>7.86270697651815</v>
+        <v>7.7908278422984232</v>
       </c>
       <c r="C18">
         <v>338.16769933532214</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-5.51374834093105</v>
+        <v>-5.6278651853369333</v>
       </c>
       <c r="B19">
-        <v>6.8814452348075879</v>
+        <v>6.7884344839181043</v>
       </c>
       <c r="C19">
         <v>338.16769933532214</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-6.7706985322182067</v>
+        <v>-6.8679125455646162</v>
       </c>
       <c r="B20">
-        <v>5.8794858130437344</v>
+        <v>5.7656300008273567</v>
       </c>
       <c r="C20">
         <v>338.16769933532214</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-8.0114051300972626</v>
+        <v>-8.0913882379969255</v>
       </c>
       <c r="B21">
-        <v>4.8577396586604236</v>
+        <v>4.7233127285704937</v>
       </c>
       <c r="C21">
         <v>338.16769933532214</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-9.2364804407072416</v>
+        <v>-9.298916935615388</v>
       </c>
       <c r="B22">
-        <v>3.8169526372767764</v>
+        <v>3.6622182064026321</v>
       </c>
       <c r="C22">
         <v>338.16769933532214</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-10.445994685361189</v>
+        <v>-10.490570278003851</v>
       </c>
       <c r="B23">
-        <v>2.7572102872530717</v>
+        <v>2.58243078842214</v>
       </c>
       <c r="C23">
         <v>338.16769933532214</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-11.639882564165639</v>
+        <v>-11.666281646396721</v>
       </c>
       <c r="B24">
-        <v>1.6784330651349009</v>
+        <v>1.4838720324382186</v>
       </c>
       <c r="C24">
         <v>338.16769933532214</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-12.818078777227145</v>
+        <v>-12.825984422028439</v>
       </c>
       <c r="B25">
-        <v>0.5805414274678341</v>
+        <v>0.36646349626004782</v>
       </c>
       <c r="C25">
         <v>338.16769933532214</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-13.980491364185451</v>
+        <v>-13.969584787201013</v>
       </c>
       <c r="B26">
-        <v>-0.53657664499249991</v>
+        <v>-0.769905288472158</v>
       </c>
       <c r="C26">
         <v>338.16769933532214</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-15.126921722813183</v>
+        <v>-15.096880128486937</v>
       </c>
       <c r="B27">
-        <v>-1.6731630746503694</v>
+        <v>-1.9254728947941704</v>
       </c>
       <c r="C27">
         <v>338.16769933532214</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-16.257144590416168</v>
+        <v>-16.207640633526307</v>
       </c>
       <c r="B28">
-        <v>-2.8294922596999856</v>
+        <v>-3.1005099219107262</v>
       </c>
       <c r="C28">
         <v>338.16769933532214</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-17.370934704300225</v>
+        <v>-17.301636489959197</v>
       </c>
       <c r="B29">
-        <v>-4.0058385983355551</v>
+        <v>-4.295286969026562</v>
       </c>
       <c r="C29">
         <v>338.16769933532214</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-18.468158258859663</v>
+        <v>-18.378731189687251</v>
       </c>
       <c r="B30">
-        <v>-5.2023650825550076</v>
+        <v>-5.5099647715471916</v>
       </c>
       <c r="C30">
         <v>338.16769933532214</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-19.549047276842657</v>
+        <v>-19.439161441658243</v>
       </c>
       <c r="B31">
-        <v>-6.4187890795710691</v>
+        <v>-6.7442646096811485</v>
       </c>
       <c r="C31">
         <v>338.16769933532214</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-20.613925238085876</v>
+        <v>-20.483257259081515</v>
       </c>
       <c r="B32">
-        <v>-7.6547165504002015</v>
+        <v>-7.9977978998377539</v>
       </c>
       <c r="C32">
         <v>338.16769933532214</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-21.663115622425988</v>
+        <v>-21.511348655166394</v>
       </c>
       <c r="B33">
-        <v>-8.9097534560588532</v>
+        <v>-9.2701760584263191</v>
       </c>
       <c r="C33">
         <v>338.16769933532214</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-22.696778701014946</v>
+        <v>-22.523599138086272</v>
       </c>
       <c r="B34">
-        <v>-10.183704566196743</v>
+        <v>-10.561206558022681</v>
       </c>
       <c r="C34">
         <v>338.16769933532214</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-23.714421910265973</v>
+        <v>-23.519506195870857</v>
       </c>
       <c r="B35">
-        <v>-11.477169884996766</v>
+        <v>-11.871481095868864</v>
       </c>
       <c r="C35">
         <v>338.16769933532214</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-24.715389477907578</v>
+        <v>-24.498400811513896</v>
       </c>
       <c r="B36">
-        <v>-12.79094822527507</v>
+        <v>-13.201787425373402</v>
       </c>
       <c r="C36">
         <v>338.16769933532214</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-25.6990256316683</v>
+        <v>-25.459613968009172</v>
       </c>
       <c r="B37">
-        <v>-14.125838399847842</v>
+        <v>-14.552913299944862</v>
       </c>
       <c r="C37">
         <v>338.16769933532214</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-26.664283582840547</v>
+        <v>-26.402077734494462</v>
       </c>
       <c r="B38">
-        <v>-15.483115528557445</v>
+        <v>-15.926116185640126</v>
       </c>
       <c r="C38">
         <v>338.16769933532214</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-27.608552476972349</v>
+        <v>-27.323128524683565</v>
       </c>
       <c r="B39">
-        <v>-16.865959959351009</v>
+        <v>-17.324532399109383</v>
       </c>
       <c r="C39">
         <v>338.16769933532214</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-28.528830443175625</v>
+        <v>-28.21970383843431</v>
       </c>
       <c r="B40">
-        <v>-18.278028347201865</v>
+        <v>-18.751767969651162</v>
       </c>
       <c r="C40">
         <v>338.16769933532214</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-29.4221156105623</v>
+        <v>-29.088741175604508</v>
       </c>
       <c r="B41">
-        <v>-19.722977347083336</v>
+        <v>-20.211428926563975</v>
       </c>
       <c r="C41">
         <v>338.16769933532214</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-29.4221156105623</v>
+        <v>-29.088741175604508</v>
       </c>
       <c r="B42">
-        <v>-19.722977347083336</v>
+        <v>-20.211428926563975</v>
       </c>
       <c r="C42">
         <v>338.16769933532214</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-28.394553247553336</v>
+        <v>-28.082714625367856</v>
       </c>
       <c r="B43">
-        <v>-18.441594800751755</v>
+        <v>-18.913069877558378</v>
       </c>
       <c r="C43">
         <v>338.16769933532214</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-27.363059132108</v>
+        <v>-27.07267691247819</v>
       </c>
       <c r="B44">
-        <v>-17.165001621663588</v>
+        <v>-17.619433887940975</v>
       </c>
       <c r="C44">
         <v>338.16769933532214</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-26.324951982538096</v>
+        <v>-26.055892600983253</v>
       </c>
       <c r="B45">
-        <v>-15.896463946966522</v>
+        <v>-16.333741875827748</v>
       </c>
       <c r="C45">
         <v>338.16769933532214</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-25.277550517155426</v>
+        <v>-25.029626254930758</v>
       </c>
       <c r="B46">
-        <v>-14.639247913808225</v>
+        <v>-15.059214759334688</v>
       </c>
       <c r="C46">
         <v>338.16769933532214</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-24.218551210769572</v>
+        <v>-23.991527824473067</v>
       </c>
       <c r="B47">
-        <v>-13.396159504576952</v>
+        <v>-13.798619672571244</v>
       </c>
       <c r="C47">
         <v>338.16769933532214</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-23.147161564181243</v>
+        <v>-22.940788804181071</v>
       </c>
       <c r="B48">
-        <v>-12.16816408262326</v>
+        <v>-12.552908613620694</v>
       </c>
       <c r="C48">
         <v>338.16769933532214</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-22.062966834688918</v>
+        <v>-21.876986074730272</v>
       </c>
       <c r="B49">
-        <v>-10.955766856538274</v>
+        <v>-11.322579796559769</v>
       </c>
       <c r="C49">
         <v>338.16769933532214</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-20.965552279591087</v>
+        <v>-20.799696516796189</v>
       </c>
       <c r="B50">
-        <v>-9.7594730349131424</v>
+        <v>-10.10813143546523</v>
       </c>
       <c r="C50">
         <v>338.16769933532214</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-19.854653315595968</v>
+        <v>-19.708650203257069</v>
       </c>
       <c r="B51">
-        <v>-8.5796049133581072</v>
+        <v>-8.90988136382746</v>
       </c>
       <c r="C51">
         <v>338.16769933532214</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-18.730605997050713</v>
+        <v>-18.604189975802075</v>
       </c>
       <c r="B52">
-        <v>-7.415753135559858</v>
+        <v>-7.727425892791449</v>
       </c>
       <c r="C52">
         <v>338.16769933532214</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-17.593896537712194</v>
+        <v>-17.486811868323095</v>
       </c>
       <c r="B53">
-        <v>-6.2673254322241911</v>
+        <v>-6.5601809529158439</v>
       </c>
       <c r="C53">
         <v>338.16769933532214</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-16.44501115133728</v>
+        <v>-16.357011914712011</v>
       </c>
       <c r="B54">
-        <v>-5.1337295340568829</v>
+        <v>-5.4075624747592652</v>
       </c>
       <c r="C54">
         <v>338.16769933532214</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-15.28433330774635</v>
+        <v>-15.21518132978893</v>
       </c>
       <c r="B55">
-        <v>-4.014498326755537</v>
+        <v>-4.2691098111257162</v>
       </c>
       <c r="C55">
         <v>338.16769933532214</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-14.11183550101379</v>
+        <v>-14.061292052086756</v>
       </c>
       <c r="B56">
-        <v>-2.9096653159849253</v>
+        <v>-3.144856003800574</v>
       </c>
       <c r="C56">
         <v>338.16769933532214</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-12.927387481277492</v>
+        <v>-12.895211201066633</v>
       </c>
       <c r="B57">
-        <v>-1.8193891624016392</v>
+        <v>-2.034957516814587</v>
       </c>
       <c r="C57">
         <v>338.16769933532214</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-11.730858998675352</v>
+        <v>-11.716805896189685</v>
       </c>
       <c r="B58">
-        <v>-0.74382852666225741</v>
+        <v>-0.93957081419849486</v>
       </c>
       <c r="C58">
         <v>338.16769933532214</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-10.522135899236366</v>
+        <v>-10.525959677899374</v>
       </c>
       <c r="B59">
-        <v>0.31687753738939095</v>
+        <v>0.14116697537721462</v>
       </c>
       <c r="C59">
         <v>338.16769933532214</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-9.3011684125540928</v>
+        <v>-9.3226217705686025</v>
       </c>
       <c r="B60">
-        <v>1.3626684031603784</v>
+        <v>1.2071960646829671</v>
       </c>
       <c r="C60">
         <v>338.16769933532214</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-8.067922864113191</v>
+        <v>-8.1067578195525911</v>
       </c>
       <c r="B61">
-        <v>2.3935030508705348</v>
+        <v>2.2584760018494472</v>
       </c>
       <c r="C61">
         <v>338.16769933532214</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-6.8223655793983422</v>
+        <v>-6.8783334702065924</v>
       </c>
       <c r="B62">
-        <v>3.4093404607396707</v>
+        <v>3.2949663350073237</v>
       </c>
       <c r="C62">
         <v>338.16769933532214</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.564587648627815</v>
+        <v>-5.6374416525122086</v>
       </c>
       <c r="B63">
-        <v>4.4102915920702062</v>
+        <v>4.3167764872491157</v>
       </c>
       <c r="C63">
         <v>338.16769933532214</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.2951792209543038</v>
+        <v>-4.38468443495653</v>
       </c>
       <c r="B64">
-        <v>5.3970753204949311</v>
+        <v>5.3246153815147084</v>
       </c>
       <c r="C64">
         <v>338.16769933532214</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.0148552102641157</v>
+        <v>-3.1207911706530309</v>
       </c>
       <c r="B65">
-        <v>6.3705625007292195</v>
+        <v>6.3193418157058163</v>
       </c>
       <c r="C65">
         <v>338.16769933532214</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.7243305304435419</v>
+        <v>-1.8464912127151667</v>
       </c>
       <c r="B66">
-        <v>7.3316239874884577</v>
+        <v>7.3018145877241727</v>
       </c>
       <c r="C66">
         <v>338.16769933532214</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.42337105593329583</v>
+        <v>-0.56154570691324812</v>
       </c>
       <c r="B67">
-        <v>8.27997458649791</v>
+        <v>8.271752451754141</v>
       </c>
       <c r="C67">
         <v>338.16769933532214</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.892053496608273</v>
+        <v>0.73815703035505931</v>
       </c>
       <c r="B68">
-        <v>9.2107049075224019</v>
+        <v>9.2243139871106763</v>
       </c>
       <c r="C68">
         <v>338.16769933532214</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2.2250796106108175</v>
+        <v>2.055816830563991</v>
       </c>
       <c r="B69">
-        <v>10.119994320641645</v>
+        <v>10.155731459749465</v>
       </c>
       <c r="C69">
         <v>338.16769933532214</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3.5714724120735903</v>
+        <v>3.3871132873026926</v>
       </c>
       <c r="B70">
-        <v>11.013001433155429</v>
+        <v>11.071092057058502</v>
       </c>
       <c r="C70">
         <v>338.16769933532214</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4.92661498185667</v>
+        <v>4.7273362327959259</v>
       </c>
       <c r="B71">
-        <v>11.895350231225711</v>
+        <v>11.975941902208401</v>
       </c>
       <c r="C71">
         <v>338.16769933532214</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6.29173357769372</v>
+        <v>6.0777366916958906</v>
       </c>
       <c r="B72">
-        <v>12.765546979243061</v>
+        <v>12.868807940067866</v>
       </c>
       <c r="C72">
         <v>338.16769933532214</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7.6688362437425521</v>
+        <v>7.4403632649411611</v>
       </c>
       <c r="B73">
-        <v>13.621145627750284</v>
+        <v>13.747277986257286</v>
       </c>
       <c r="C73">
         <v>338.16769933532214</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>9.0572149929839263</v>
+        <v>8.8144936661883442</v>
       </c>
       <c r="B74">
-        <v>14.463008593670532</v>
+        <v>14.612202517705743</v>
       </c>
       <c r="C74">
         <v>338.16769933532214</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>10.455471028531232</v>
+        <v>10.198700846832141</v>
       </c>
       <c r="B75">
-        <v>15.292839786926246</v>
+        <v>15.46526185403518</v>
       </c>
       <c r="C75">
         <v>338.16769933532214</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>11.862158345205424</v>
+        <v>11.591509596501574</v>
       </c>
       <c r="B76">
-        <v>16.112400623056793</v>
+        <v>16.308193024330425</v>
       </c>
       <c r="C76">
         <v>338.16769933532214</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>13.275952503608426</v>
+        <v>12.991568725889659</v>
       </c>
       <c r="B77">
-        <v>16.923304435244187</v>
+        <v>17.142587025490293</v>
       </c>
       <c r="C77">
         <v>338.16769933532214</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>14.696062535758431</v>
+        <v>14.398071291711011</v>
       </c>
       <c r="B78">
-        <v>17.726514721624177</v>
+        <v>17.969394016206785</v>
       </c>
       <c r="C78">
         <v>338.16769933532214</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>16.121058360142904</v>
+        <v>15.80955832887393</v>
       </c>
       <c r="B79">
-        <v>18.523773500714569</v>
+        <v>18.790331897091157</v>
       </c>
       <c r="C79">
         <v>338.16769933532214</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>17.548345104322351</v>
+        <v>17.223382555895917</v>
       </c>
       <c r="B80">
-        <v>19.318241652368215</v>
+        <v>19.608517786231285</v>
       </c>
       <c r="C80">
         <v>338.16769933532214</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>18.971350089609526</v>
+        <v>18.632838544674065</v>
       </c>
       <c r="B81">
-        <v>20.117925522995737</v>
+        <v>20.43184718373351</v>
       </c>
       <c r="C81">
         <v>338.16769933532214</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>20.26908783120912</v>
+        <v>19.914497247723702</v>
       </c>
       <c r="B82">
-        <v>21.070200596477843</v>
+        <v>21.4056551886526</v>
       </c>
       <c r="C82">
         <v>338.16769933532214</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>20.172148976913753</v>
+        <v>19.983375521291535</v>
       </c>
       <c r="B1">
-        <v>25.39994102558904</v>
+        <v>25.548724062568184</v>
       </c>
       <c r="C1">
         <v>410.1621514722421</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>18.065291361136822</v>
+        <v>17.786735701064757</v>
       </c>
       <c r="B2">
-        <v>25.008902816503682</v>
+        <v>25.235742011603406</v>
       </c>
       <c r="C2">
         <v>410.1621514722421</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>16.265135932207436</v>
+        <v>15.956766988246569</v>
       </c>
       <c r="B3">
-        <v>24.30349426151286</v>
+        <v>24.552451307445438</v>
       </c>
       <c r="C3">
         <v>410.1621514722421</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>14.525145443063988</v>
+        <v>14.195439107649744</v>
       </c>
       <c r="B4">
-        <v>23.536416524680536</v>
+        <v>23.799838822486141</v>
       </c>
       <c r="C4">
         <v>410.1621514722421</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>12.831392657315565</v>
+        <v>12.485962352977435</v>
       </c>
       <c r="B5">
-        <v>22.721945050752385</v>
+        <v>22.994860824619781</v>
       </c>
       <c r="C5">
         <v>410.1621514722421</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>11.178075688537581</v>
+        <v>10.821367697433404</v>
       </c>
       <c r="B6">
-        <v>21.866026784746797</v>
+        <v>22.144555476589016</v>
       </c>
       <c r="C6">
         <v>410.1621514722421</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>9.5618092838562</v>
+        <v>9.1976036820354921</v>
       </c>
       <c r="B7">
-        <v>20.972131617530408</v>
+        <v>21.253014429709808</v>
       </c>
       <c r="C7">
         <v>410.1621514722421</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>7.9805309743984711</v>
+        <v>7.6122161121539591</v>
       </c>
       <c r="B8">
-        <v>20.042373583762327</v>
+        <v>20.322716225349762</v>
       </c>
       <c r="C8">
         <v>410.1621514722421</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>6.4311447593858864</v>
+        <v>6.0614966892634188</v>
       </c>
       <c r="B9">
-        <v>19.079926090341452</v>
+        <v>19.357405950058702</v>
       </c>
       <c r="C9">
         <v>410.1621514722421</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>4.9103315513854415</v>
+        <v>4.5414652754749332</v>
       </c>
       <c r="B10">
-        <v>18.088191208427233</v>
+        <v>18.361103226521383</v>
       </c>
       <c r="C10">
         <v>410.1621514722421</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>3.4149134482515535</v>
+        <v>3.0483084793408581</v>
       </c>
       <c r="B11">
-        <v>17.070426293981249</v>
+        <v>17.337659276779952</v>
       </c>
       <c r="C11">
         <v>410.1621514722421</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.9431385967751749</v>
+        <v>1.5799352113445324</v>
       </c>
       <c r="B12">
-        <v>16.028426999994966</v>
+        <v>16.289185934919445</v>
       </c>
       <c r="C12">
         <v>410.1621514722421</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.49881815420593173</v>
+        <v>0.14097684325192761</v>
       </c>
       <c r="B13">
-        <v>14.958286882777273</v>
+        <v>15.211005883838951</v>
       </c>
       <c r="C13">
         <v>410.1621514722421</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.91580451630146864</v>
+        <v>-1.2658326985127639</v>
       </c>
       <c r="B14">
-        <v>13.857706490673817</v>
+        <v>14.100358075308549</v>
       </c>
       <c r="C14">
         <v>410.1621514722421</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.310320238430652</v>
+        <v>-2.6520717301750207</v>
       </c>
       <c r="B15">
-        <v>12.736516436859976</v>
+        <v>12.968935687768184</v>
       </c>
       <c r="C15">
         <v>410.1621514722421</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.6935252195280093</v>
+        <v>-4.0283593744658148</v>
       </c>
       <c r="B16">
-        <v>11.603732851199588</v>
+        <v>11.827463190523309</v>
       </c>
       <c r="C16">
         <v>410.1621514722421</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-5.059203014752657</v>
+        <v>-5.3871657374883437</v>
       </c>
       <c r="B17">
-        <v>10.452983865480633</v>
+        <v>10.66833598967145</v>
       </c>
       <c r="C17">
         <v>410.1621514722421</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-6.3992975496526752</v>
+        <v>-6.7187386313638591</v>
       </c>
       <c r="B18">
-        <v>9.276011987514611</v>
+        <v>9.4817051511512727</v>
       </c>
       <c r="C18">
         <v>410.1621514722421</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.7134068835192231</v>
+        <v>-8.0225857089135886</v>
       </c>
       <c r="B19">
-        <v>8.0724052272828981</v>
+        <v>8.2670734434738637</v>
       </c>
       <c r="C19">
         <v>410.1621514722421</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-9.0030426090792375</v>
+        <v>-9.3005295831337484</v>
       </c>
       <c r="B20">
-        <v>6.8437129703093378</v>
+        <v>7.0262815607934277</v>
       </c>
       <c r="C20">
         <v>410.1621514722421</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-10.269716319059651</v>
+        <v>-10.554392867020555</v>
       </c>
       <c r="B21">
-        <v>5.5914846021177924</v>
+        <v>5.7611701972641747</v>
       </c>
       <c r="C21">
         <v>410.1621514722421</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-11.514666915712111</v>
+        <v>-11.785670110831958</v>
       </c>
       <c r="B22">
-        <v>4.3169899999575616</v>
+        <v>4.4732487297689856</v>
       </c>
       <c r="C22">
         <v>410.1621514722421</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-12.738042539387063</v>
+        <v>-12.994543613872782</v>
       </c>
       <c r="B23">
-        <v>3.020381007979787</v>
+        <v>3.1627012661055258</v>
       </c>
       <c r="C23">
         <v>410.1621514722421</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-13.939718639959674</v>
+        <v>-14.180867612709577</v>
       </c>
       <c r="B24">
-        <v>1.7015299620610846</v>
+        <v>1.8293805968001538</v>
       </c>
       <c r="C24">
         <v>410.1621514722421</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-15.119570667305114</v>
+        <v>-15.344496343908908</v>
       </c>
       <c r="B25">
-        <v>0.3603091980780449</v>
+        <v>0.47313951237920593</v>
       </c>
       <c r="C25">
         <v>410.1621514722421</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-16.277422584293287</v>
+        <v>-16.48522341055056</v>
       </c>
       <c r="B26">
-        <v>-1.0034617223745574</v>
+        <v>-0.9062304316297467</v>
       </c>
       <c r="C26">
         <v>410.1621514722421</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-17.41289240577311</v>
+        <v>-17.6025998817673</v>
       </c>
       <c r="B27">
-        <v>-2.3901743348293434</v>
+        <v>-2.3091826196943428</v>
       </c>
       <c r="C27">
         <v>410.1621514722421</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-18.52554665958823</v>
+        <v>-18.696116193205125</v>
       </c>
       <c r="B28">
-        <v>-3.8002729491007639</v>
+        <v>-3.7362316712809922</v>
       </c>
       <c r="C28">
         <v>410.1621514722421</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-19.614951873582303</v>
+        <v>-19.765262780510024</v>
       </c>
       <c r="B29">
-        <v>-5.2342018750032562</v>
+        <v>-5.1878922058561114</v>
       </c>
       <c r="C29">
         <v>410.1621514722421</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-20.680863287357457</v>
+        <v>-20.809759993104187</v>
       </c>
       <c r="B30">
-        <v>-6.6922119924269881</v>
+        <v>-6.6644466482596956</v>
       </c>
       <c r="C30">
         <v>410.1621514722421</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-21.723790987549677</v>
+        <v>-21.83024783551453</v>
       </c>
       <c r="B31">
-        <v>-8.17378046156488</v>
+        <v>-8.16524864482597</v>
       </c>
       <c r="C31">
         <v>410.1621514722421</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-22.744433772553418</v>
+        <v>-22.827596226044157</v>
       </c>
       <c r="B32">
-        <v>-9.6781910126855752</v>
+        <v>-9.6894196472627563</v>
       </c>
       <c r="C32">
         <v>410.1621514722421</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-23.743490440763139</v>
+        <v>-23.802675082996181</v>
       </c>
       <c r="B33">
-        <v>-11.20472737605771</v>
+        <v>-11.236081107277851</v>
       </c>
       <c r="C33">
         <v>410.1621514722421</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-24.721331103670643</v>
+        <v>-24.7559589700979</v>
       </c>
       <c r="B34">
-        <v>-12.753010186672825</v>
+        <v>-12.804753753253817</v>
       </c>
       <c r="C34">
         <v>410.1621514722421</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-25.677011125157197</v>
+        <v>-25.686341032773445</v>
       </c>
       <c r="B35">
-        <v>-14.324007698414135</v>
+        <v>-14.396555420272273</v>
       </c>
       <c r="C35">
         <v>410.1621514722421</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-26.609257182201407</v>
+        <v>-26.592319061871141</v>
       </c>
       <c r="B36">
-        <v>-15.91902506988777</v>
+        <v>-16.013003220089576</v>
       </c>
       <c r="C36">
         <v>410.1621514722421</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-27.516795951781894</v>
+        <v>-27.472390848239311</v>
       </c>
       <c r="B37">
-        <v>-17.539367459699854</v>
+        <v>-17.655614264462113</v>
       </c>
       <c r="C37">
         <v>410.1621514722421</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-28.397562200305948</v>
+        <v>-28.324098828428792</v>
       </c>
       <c r="B38">
-        <v>-19.187151736352661</v>
+        <v>-19.326870496997127</v>
       </c>
       <c r="C38">
         <v>410.1621514722421</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-29.24632305189559</v>
+        <v>-29.141164021800403</v>
       </c>
       <c r="B39">
-        <v>-20.86774160793302</v>
+        <v>-21.033113188705453</v>
       </c>
       <c r="C39">
         <v>410.1621514722421</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-30.057053720101518</v>
+        <v>-29.916352093417466</v>
       </c>
       <c r="B40">
-        <v>-22.587312492423887</v>
+        <v>-22.781648442448823</v>
       </c>
       <c r="C40">
         <v>410.1621514722421</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-30.823729418474414</v>
+        <v>-30.6424287083433</v>
       </c>
       <c r="B41">
-        <v>-24.352039807808229</v>
+        <v>-24.579782361088938</v>
       </c>
       <c r="C41">
         <v>410.1621514722421</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-30.823729418474414</v>
+        <v>-30.6424287083433</v>
       </c>
       <c r="B42">
-        <v>-24.352039807808229</v>
+        <v>-24.579782361088938</v>
       </c>
       <c r="C42">
         <v>410.1621514722421</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-29.784109533526767</v>
+        <v>-29.586340282490873</v>
       </c>
       <c r="B43">
-        <v>-22.867080821526287</v>
+        <v>-23.114934122102596</v>
       </c>
       <c r="C43">
         <v>410.1621514722421</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-28.747310684136618</v>
+        <v>-28.537817318485267</v>
       </c>
       <c r="B44">
-        <v>-21.379230268238761</v>
+        <v>-21.642445368413338</v>
       </c>
       <c r="C44">
         <v>410.1621514722421</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-27.707805557754462</v>
+        <v>-27.49012672019807</v>
       </c>
       <c r="B45">
-        <v>-19.894153654201023</v>
+        <v>-20.169115991555476</v>
       </c>
       <c r="C45">
         <v>410.1621514722421</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-26.66006684183079</v>
+        <v>-26.436535391500861</v>
       </c>
       <c r="B46">
-        <v>-18.417516485668436</v>
+        <v>-18.701745883063289</v>
       </c>
       <c r="C46">
         <v>410.1621514722421</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-25.599337991867358</v>
+        <v>-25.371244288034969</v>
       </c>
       <c r="B47">
-        <v>-16.954194230124948</v>
+        <v>-17.246191616478782</v>
       </c>
       <c r="C47">
         <v>410.1621514722421</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-24.523945535570942</v>
+        <v>-24.292190572520685</v>
       </c>
       <c r="B48">
-        <v>-15.505902199968842</v>
+        <v>-15.804536493374876</v>
       </c>
       <c r="C48">
         <v>410.1621514722421</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-23.432986768699575</v>
+        <v>-23.198245459448049</v>
       </c>
       <c r="B49">
-        <v>-14.073565668826992</v>
+        <v>-14.377920497332191</v>
       </c>
       <c r="C49">
         <v>410.1621514722421</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-22.32555898701132</v>
+        <v>-22.088280163307108</v>
       </c>
       <c r="B50">
-        <v>-12.658109910326273</v>
+        <v>-12.967483611931362</v>
       </c>
       <c r="C50">
         <v>410.1621514722421</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-21.201067780192393</v>
+        <v>-20.961540705854155</v>
       </c>
       <c r="B51">
-        <v>-11.260144196209629</v>
+        <v>-11.573987295226536</v>
       </c>
       <c r="C51">
         <v>410.1621514722421</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-20.060151913641853</v>
+        <v>-19.818772337910531</v>
       </c>
       <c r="B52">
-        <v>-9.8790137906842972</v>
+        <v>-10.196678903165953</v>
       </c>
       <c r="C52">
         <v>410.1621514722421</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-18.903758446686936</v>
+        <v>-18.661095117563843</v>
       </c>
       <c r="B53">
-        <v>-8.5137479560735869</v>
+        <v>-8.8344272661713958</v>
       </c>
       <c r="C53">
         <v>410.1621514722421</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-17.732834438654884</v>
+        <v>-17.489629102901688</v>
       </c>
       <c r="B54">
-        <v>-7.16337595470079</v>
+        <v>-7.4861012146646146</v>
       </c>
       <c r="C54">
         <v>410.1621514722421</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-16.548120909753958</v>
+        <v>-16.3052469797406</v>
       </c>
       <c r="B55">
-        <v>-5.8271382393921982</v>
+        <v>-6.1508194053849916</v>
       </c>
       <c r="C55">
         <v>410.1621514722421</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-15.349534723716515</v>
+        <v>-15.107831944812862</v>
       </c>
       <c r="B56">
-        <v>-4.505120024985958</v>
+        <v>-4.8286998003422976</v>
       </c>
       <c r="C56">
         <v>410.1621514722421</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-14.136786705155936</v>
+        <v>-13.897019822579685</v>
       </c>
       <c r="B57">
-        <v>-3.1976177168232125</v>
+        <v>-3.52011018786392</v>
       </c>
       <c r="C57">
         <v>410.1621514722421</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-12.909587678685607</v>
+        <v>-12.672446437502288</v>
       </c>
       <c r="B58">
-        <v>-1.9049277202450978</v>
+        <v>-2.225418356277248</v>
       </c>
       <c r="C58">
         <v>410.1621514722421</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-11.667683892422009</v>
+        <v>-11.433792062457073</v>
       </c>
       <c r="B59">
-        <v>-0.627310131432246</v>
+        <v>-0.94494720454577075</v>
       </c>
       <c r="C59">
         <v>410.1621514722421</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-10.410963288494065</v>
+        <v>-10.180914763981217</v>
       </c>
       <c r="B60">
-        <v>0.63512019007665</v>
+        <v>0.3211599258225416</v>
       </c>
       <c r="C60">
         <v>410.1621514722421</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-9.1393492325337888</v>
+        <v>-8.9137170570270836</v>
       </c>
       <c r="B61">
-        <v>1.8822846939034088</v>
+        <v>1.5728045826836195</v>
       </c>
       <c r="C61">
         <v>410.1621514722421</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-7.8527650901732118</v>
+        <v>-7.6321014565470406</v>
       </c>
       <c r="B62">
-        <v>3.1141048296698361</v>
+        <v>2.8098883138933815</v>
       </c>
       <c r="C62">
         <v>410.1621514722421</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-6.5513906177273995</v>
+        <v>-6.3362821170818009</v>
       </c>
       <c r="B63">
-        <v>4.3307648479530911</v>
+        <v>4.0326273985039283</v>
       </c>
       <c r="C63">
         <v>410.1621514722421</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-5.2364311342435546</v>
+        <v>-5.0277197515254244</v>
       </c>
       <c r="B64">
-        <v>5.533500203151779</v>
+        <v>5.2424970403521005</v>
       </c>
       <c r="C64">
         <v>410.1621514722421</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.9093483494519377</v>
+        <v>-3.7081867123603272</v>
       </c>
       <c r="B65">
-        <v>6.7238091506198385</v>
+        <v>6.4412871744709062</v>
       </c>
       <c r="C65">
         <v>410.1621514722421</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.5716039730827953</v>
+        <v>-2.3794553520689168</v>
       </c>
       <c r="B66">
-        <v>7.9031899457112242</v>
+        <v>7.63078773589336</v>
       </c>
       <c r="C66">
         <v>410.1621514722421</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.2227328623615301</v>
+        <v>-1.0409696430901221</v>
       </c>
       <c r="B67">
-        <v>9.0711658161653688</v>
+        <v>8.8104371810096289</v>
       </c>
       <c r="C67">
         <v>410.1621514722421</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.14543753550583671</v>
+        <v>0.31713996231103742</v>
       </c>
       <c r="B68">
-        <v>10.219359879263616</v>
+        <v>9.9702680516384525</v>
       </c>
       <c r="C68">
         <v>410.1621514722421</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.5392596803172907</v>
+        <v>1.7025404023567665</v>
       </c>
       <c r="B69">
-        <v>11.341260851194891</v>
+        <v>11.102537350009316</v>
       </c>
       <c r="C69">
         <v>410.1621514722421</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.9500982498674158</v>
+        <v>3.1047746570442309</v>
       </c>
       <c r="B70">
-        <v>12.445719954236497</v>
+        <v>12.217805834566022</v>
       </c>
       <c r="C70">
         <v>410.1621514722421</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4.3685388137244514</v>
+        <v>4.5124421383531494</v>
       </c>
       <c r="B71">
-        <v>13.542386998133043</v>
+        <v>13.327587192397898</v>
       </c>
       <c r="C71">
         <v>410.1621514722421</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5.7970382905546147</v>
+        <v>5.9284919444185018</v>
       </c>
       <c r="B72">
-        <v>14.628743636410063</v>
+        <v>14.428903068962054</v>
       </c>
       <c r="C72">
         <v>410.1621514722421</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7.2396397963496515</v>
+        <v>7.3577891612242539</v>
       </c>
       <c r="B73">
-        <v>15.700645667208656</v>
+        <v>15.516840114387195</v>
       </c>
       <c r="C73">
         <v>410.1621514722421</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8.6948598873054639</v>
+        <v>8.7985131399950962</v>
       </c>
       <c r="B74">
-        <v>16.759613623351289</v>
+        <v>16.593237039120641</v>
       </c>
       <c r="C74">
         <v>410.1621514722421</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>10.159808004273785</v>
+        <v>10.247140006907522</v>
       </c>
       <c r="B75">
-        <v>17.808610333661079</v>
+        <v>17.661652675432631</v>
       </c>
       <c r="C75">
         <v>410.1621514722421</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>11.631491686525529</v>
+        <v>11.700018722704456</v>
       </c>
       <c r="B76">
-        <v>18.850703076282262</v>
+        <v>18.725774282566437</v>
       </c>
       <c r="C76">
         <v>410.1621514722421</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>13.107162495350247</v>
+        <v>13.153791181296475</v>
       </c>
       <c r="B77">
-        <v>19.888709006309128</v>
+        <v>19.788993280566178</v>
       </c>
       <c r="C77">
         <v>410.1621514722421</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>14.585149981692819</v>
+        <v>14.606398174698132</v>
       </c>
       <c r="B78">
-        <v>20.924340337314952</v>
+        <v>20.853389305706227</v>
       </c>
       <c r="C78">
         <v>410.1621514722421</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>16.062481650815965</v>
+        <v>16.054204125838954</v>
       </c>
       <c r="B79">
-        <v>21.960643882263042</v>
+        <v>21.922634001651282</v>
       </c>
       <c r="C79">
         <v>410.1621514722421</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>17.533811443459065</v>
+        <v>17.490699284810475</v>
       </c>
       <c r="B80">
-        <v>23.003099362430461</v>
+        <v>23.003301698018607</v>
       </c>
       <c r="C80">
         <v>410.1621514722421</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>18.985703006554672</v>
+        <v>18.899588543669946</v>
       </c>
       <c r="B81">
-        <v>24.065479066189</v>
+        <v>24.111849157705514</v>
       </c>
       <c r="C81">
         <v>410.1621514722421</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>20.172148976913753</v>
+        <v>19.983375521291535</v>
       </c>
       <c r="B82">
-        <v>25.39994102558904</v>
+        <v>25.548724062568184</v>
       </c>
       <c r="C82">
         <v>410.1621514722421</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>20.069389397282226</v>
+        <v>19.999288131866013</v>
       </c>
       <c r="B1">
-        <v>28.84645348988775</v>
+        <v>28.895145690768942</v>
       </c>
       <c r="C1">
         <v>471.28397822006644</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>17.592364567683155</v>
+        <v>17.31153596634303</v>
       </c>
       <c r="B2">
-        <v>28.492712871375446</v>
+        <v>28.727012933738582</v>
       </c>
       <c r="C2">
         <v>471.28397822006644</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>15.59921782604707</v>
+        <v>15.240255671448717</v>
       </c>
       <c r="B3">
-        <v>27.698668252761003</v>
+        <v>28.00064443546885</v>
       </c>
       <c r="C3">
         <v>471.28397822006644</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>13.694179784563277</v>
+        <v>13.275577629820095</v>
       </c>
       <c r="B4">
-        <v>26.824449280138989</v>
+        <v>27.1777440584471</v>
       </c>
       <c r="C4">
         <v>471.28397822006644</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>11.854971687914127</v>
+        <v>11.388883543160716</v>
       </c>
       <c r="B5">
-        <v>25.890328467036415</v>
+        <v>26.284226621700249</v>
       </c>
       <c r="C5">
         <v>471.28397822006644</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>10.072355830005494</v>
+        <v>9.56835261623153</v>
       </c>
       <c r="B6">
-        <v>24.9047116475801</v>
+        <v>25.330796247681725</v>
       </c>
       <c r="C6">
         <v>471.28397822006644</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>8.3409678103438889</v>
+        <v>7.8071470842808379</v>
       </c>
       <c r="B7">
-        <v>23.872480148397919</v>
+        <v>24.323644759338283</v>
       </c>
       <c r="C7">
         <v>471.28397822006644</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>6.65756377287935</v>
+        <v>6.1011578060639318</v>
       </c>
       <c r="B8">
-        <v>22.796585710496746</v>
+        <v>23.26649312046063</v>
       </c>
       <c r="C8">
         <v>471.28397822006644</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>5.01723295390029</v>
+        <v>4.4441196543918755</v>
       </c>
       <c r="B9">
-        <v>21.681496874526683</v>
+        <v>22.165014611675026</v>
       </c>
       <c r="C9">
         <v>471.28397822006644</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.4147028738956053</v>
+        <v>2.829297608347261</v>
       </c>
       <c r="B10">
-        <v>20.53201132378225</v>
+        <v>21.025308017975934</v>
       </c>
       <c r="C10">
         <v>471.28397822006644</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.8449210978176545</v>
+        <v>1.2502330580429297</v>
       </c>
       <c r="B11">
-        <v>19.352726512492243</v>
+        <v>19.853221824995064</v>
       </c>
       <c r="C11">
         <v>471.28397822006644</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.30512173928060915</v>
+        <v>-0.29658972008539053</v>
       </c>
       <c r="B12">
-        <v>18.146159254023097</v>
+        <v>18.651939637116339</v>
       </c>
       <c r="C12">
         <v>471.28397822006644</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.1985349379176162</v>
+        <v>-1.8031913153407093</v>
       </c>
       <c r="B13">
-        <v>16.90670402735747</v>
+        <v>17.414235833095198</v>
       </c>
       <c r="C13">
         <v>471.28397822006644</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.6624092234272716</v>
+        <v>-3.264843476900579</v>
       </c>
       <c r="B14">
-        <v>15.631048884576934</v>
+        <v>16.135828824868359</v>
       </c>
       <c r="C14">
         <v>471.28397822006644</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.101869770875064</v>
+        <v>-4.7013177277020013</v>
       </c>
       <c r="B15">
-        <v>14.333178504542447</v>
+        <v>14.834622382726117</v>
       </c>
       <c r="C15">
         <v>471.28397822006644</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-5.5310120392313369</v>
+        <v>-6.1307478163925353</v>
       </c>
       <c r="B16">
-        <v>13.025919024916176</v>
+        <v>13.527037217977487</v>
       </c>
       <c r="C16">
         <v>471.28397822006644</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-6.9398303448646033</v>
+        <v>-7.5402166207025507</v>
       </c>
       <c r="B17">
-        <v>11.700165791785715</v>
+        <v>12.201376447652754</v>
       </c>
       <c r="C17">
         <v>471.28397822006644</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-8.3153685932022938</v>
+        <v>-8.9130087943597722</v>
       </c>
       <c r="B18">
-        <v>10.344129430083431</v>
+        <v>10.842503770874371</v>
       </c>
       <c r="C18">
         <v>471.28397822006644</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-9.6569701885092822</v>
+        <v>-10.248266965998523</v>
       </c>
       <c r="B19">
-        <v>8.957212471695323</v>
+        <v>9.4496428094122251</v>
       </c>
       <c r="C19">
         <v>471.28397822006644</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-10.967053409759819</v>
+        <v>-11.549098257979789</v>
       </c>
       <c r="B20">
-        <v>7.5416154252457828</v>
+        <v>8.0256071656980534</v>
       </c>
       <c r="C20">
         <v>471.28397822006644</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-12.248036535928144</v>
+        <v>-12.81860979266453</v>
       </c>
       <c r="B21">
-        <v>6.09953879935923</v>
+        <v>6.573210442163604</v>
       </c>
       <c r="C21">
         <v>471.28397822006644</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-13.501902886209955</v>
+        <v>-14.059351146917958</v>
       </c>
       <c r="B22">
-        <v>4.6327873117880465</v>
+        <v>5.0947613652877246</v>
       </c>
       <c r="C22">
         <v>471.28397822006644</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-14.728895940686705</v>
+        <v>-15.271641715622158</v>
       </c>
       <c r="B23">
-        <v>3.1415825167965954</v>
+        <v>3.5905491577377493</v>
       </c>
       <c r="C23">
         <v>471.28397822006644</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-15.928824219661317</v>
+        <v>-16.455243348163453</v>
       </c>
       <c r="B24">
-        <v>1.6257501777772057</v>
+        <v>2.0603581662281112</v>
       </c>
       <c r="C24">
         <v>471.28397822006644</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-17.101496243436696</v>
+        <v>-17.60991789392817</v>
       </c>
       <c r="B25">
-        <v>0.085116058122227181</v>
+        <v>0.50397273747325966</v>
       </c>
       <c r="C25">
         <v>471.28397822006644</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-18.246640697123812</v>
+        <v>-18.735327211892642</v>
       </c>
       <c r="B26">
-        <v>-1.4805667246659982</v>
+        <v>-1.0789133264475312</v>
       </c>
       <c r="C26">
         <v>471.28397822006644</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-19.363666925065932</v>
+        <v>-19.8307331993934</v>
       </c>
       <c r="B27">
-        <v>-3.0718356366452038</v>
+        <v>-2.6889684019957212</v>
       </c>
       <c r="C27">
         <v>471.28397822006644</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-20.45190443641437</v>
+        <v>-20.895297763356972</v>
       </c>
       <c r="B28">
-        <v>-4.6893007897630969</v>
+        <v>-4.3269514102679105</v>
       </c>
       <c r="C28">
         <v>471.28397822006644</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-21.510682740320441</v>
+        <v>-21.928182810709892</v>
       </c>
       <c r="B29">
-        <v>-6.3335722959673939</v>
+        <v>-5.9936212723607181</v>
       </c>
       <c r="C29">
         <v>471.28397822006644</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-22.539637369986938</v>
+        <v>-22.928947693729476</v>
       </c>
       <c r="B30">
-        <v>-8.0049818011679</v>
+        <v>-7.6893770094133549</v>
       </c>
       <c r="C30">
         <v>471.28397822006644</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-23.539627954822564</v>
+        <v>-23.898741546096044</v>
       </c>
       <c r="B31">
-        <v>-9.7027470871227237</v>
+        <v>-9.4131780427353817</v>
       </c>
       <c r="C31">
         <v>471.28397822006644</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-24.511820148287477</v>
+        <v>-24.839110946840687</v>
       </c>
       <c r="B32">
-        <v>-11.425807469552057</v>
+        <v>-11.163623893678979</v>
       </c>
       <c r="C32">
         <v>471.28397822006644</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-25.457379603841861</v>
+        <v>-25.7516024749945</v>
       </c>
       <c r="B33">
-        <v>-13.173102264176103</v>
+        <v>-12.93931408359631</v>
       </c>
       <c r="C33">
         <v>471.28397822006644</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-26.376947655676961</v>
+        <v>-26.637090803295</v>
       </c>
       <c r="B34">
-        <v>-14.944047890095364</v>
+        <v>-14.739456567290764</v>
       </c>
       <c r="C34">
         <v>471.28397822006644</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-27.269068360908403</v>
+        <v>-27.493762979305398</v>
       </c>
       <c r="B35">
-        <v>-16.739969179931673</v>
+        <v>-16.56569303337071</v>
       </c>
       <c r="C35">
         <v>471.28397822006644</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-28.131761457382865</v>
+        <v>-28.319134144295333</v>
       </c>
       <c r="B36">
-        <v>-18.56266806968716</v>
+        <v>-18.420273603895716</v>
       </c>
       <c r="C36">
         <v>471.28397822006644</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-28.963046682947063</v>
+        <v>-29.11071943953446</v>
       </c>
       <c r="B37">
-        <v>-20.413946495363984</v>
+        <v>-20.305448400925386</v>
       </c>
       <c r="C37">
         <v>471.28397822006644</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-29.759675676273353</v>
+        <v>-29.864403878013235</v>
       </c>
       <c r="B38">
-        <v>-22.296760297538349</v>
+        <v>-22.224943681784513</v>
       </c>
       <c r="C38">
         <v>471.28397822006644</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-30.5133276793367</v>
+        <v>-30.569551959605427</v>
       </c>
       <c r="B39">
-        <v>-24.218680935082716</v>
+        <v>-24.188390244858684</v>
       </c>
       <c r="C39">
         <v>471.28397822006644</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-31.214413834937755</v>
+        <v>-31.21389805590562</v>
       </c>
       <c r="B40">
-        <v>-26.188433771443613</v>
+        <v>-26.206895023798715</v>
       </c>
       <c r="C40">
         <v>471.28397822006644</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-31.85334528587714</v>
+        <v>-31.785176538508402</v>
       </c>
       <c r="B41">
-        <v>-28.214744170067565</v>
+        <v>-28.291564952255403</v>
       </c>
       <c r="C41">
         <v>471.28397822006644</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-31.85334528587714</v>
+        <v>-31.785176538508402</v>
       </c>
       <c r="B42">
-        <v>-28.214744170067565</v>
+        <v>-28.291564952255403</v>
       </c>
       <c r="C42">
         <v>471.28397822006644</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-30.776153273505965</v>
+        <v>-30.649180753716067</v>
       </c>
       <c r="B43">
-        <v>-26.587228184924442</v>
+        <v>-26.718265285440982</v>
       </c>
       <c r="C43">
         <v>471.28397822006644</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-29.71207434179561</v>
+        <v>-29.537103085656266</v>
       </c>
       <c r="B44">
-        <v>-24.947779975503639</v>
+        <v>-25.123306970017623</v>
       </c>
       <c r="C44">
         <v>471.28397822006644</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-28.652148393096958</v>
+        <v>-28.437308048506257</v>
       </c>
       <c r="B45">
-        <v>-23.304552766624308</v>
+        <v>-23.517226324611382</v>
       </c>
       <c r="C45">
         <v>471.28397822006644</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-27.587415329760862</v>
+        <v>-27.33816015644328</v>
       </c>
       <c r="B46">
-        <v>-21.665699783105591</v>
+        <v>-21.910559667848315</v>
       </c>
       <c r="C46">
         <v>471.28397822006644</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-26.510156114140539</v>
+        <v>-26.229626953275844</v>
       </c>
       <c r="B47">
-        <v>-20.038244949438734</v>
+        <v>-20.312391721814439</v>
       </c>
       <c r="C47">
         <v>471.28397822006644</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-25.417615948598602</v>
+        <v>-25.108088101337511</v>
       </c>
       <c r="B48">
-        <v>-18.424694988803388</v>
+        <v>-18.72600082243564</v>
       </c>
       <c r="C48">
         <v>471.28397822006644</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-24.308281095499986</v>
+        <v>-23.971526292593076</v>
       </c>
       <c r="B49">
-        <v>-16.826427324051277</v>
+        <v>-17.15321370909772</v>
       </c>
       <c r="C49">
         <v>471.28397822006644</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-23.180637817209643</v>
+        <v>-22.817924219007349</v>
       </c>
       <c r="B50">
-        <v>-15.244819378034162</v>
+        <v>-15.595857121186517</v>
       </c>
       <c r="C50">
         <v>471.28397822006644</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-22.0336708431304</v>
+        <v>-21.64591056974259</v>
       </c>
       <c r="B51">
-        <v>-13.680794994414807</v>
+        <v>-14.055172826183162</v>
       </c>
       <c r="C51">
         <v>471.28397822006644</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-20.868358770816567</v>
+        <v>-20.456698022750789</v>
       </c>
       <c r="B52">
-        <v>-12.133463700100165</v>
+        <v>-12.530062703950035</v>
       </c>
       <c r="C52">
         <v>471.28397822006644</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-19.686178664860336</v>
+        <v>-19.252145253181382</v>
       </c>
       <c r="B53">
-        <v>-10.601481442808199</v>
+        <v>-11.018843662444821</v>
       </c>
       <c r="C53">
         <v>471.28397822006644</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-18.488607589853885</v>
+        <v>-18.034110936183797</v>
       </c>
       <c r="B54">
-        <v>-9.08350417025688</v>
+        <v>-9.5198326096251922</v>
       </c>
       <c r="C54">
         <v>471.28397822006644</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-17.276794791517375</v>
+        <v>-16.804034458795819</v>
       </c>
       <c r="B55">
-        <v>-7.5784861283600753</v>
+        <v>-8.031726132751265</v>
       </c>
       <c r="C55">
         <v>471.28397822006644</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-16.050578240082803</v>
+        <v>-15.561678055608603</v>
       </c>
       <c r="B56">
-        <v>-6.0865747558151568</v>
+        <v>-6.5547395362928151</v>
       </c>
       <c r="C56">
         <v>471.28397822006644</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-14.809468086910153</v>
+        <v>-14.306384673101663</v>
       </c>
       <c r="B57">
-        <v>-4.6082157895154019</v>
+        <v>-5.0894678040220533</v>
       </c>
       <c r="C57">
         <v>471.28397822006644</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-13.552974483359394</v>
+        <v>-13.037497257754515</v>
       </c>
       <c r="B58">
-        <v>-3.1438549663540867</v>
+        <v>-3.6365059197111971</v>
       </c>
       <c r="C58">
         <v>471.28397822006644</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-12.280667295917123</v>
+        <v>-11.754438582134805</v>
       </c>
       <c r="B59">
-        <v>-1.6938836855518551</v>
+        <v>-2.19637658195996</v>
       </c>
       <c r="C59">
         <v>471.28397822006644</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-10.992355251576486</v>
+        <v>-10.456950723162832</v>
       </c>
       <c r="B60">
-        <v>-0.25847599563896817</v>
+        <v>-0.76931334867820156</v>
       </c>
       <c r="C60">
         <v>471.28397822006644</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-9.6879067924572784</v>
+        <v>-9.144855583847054</v>
       </c>
       <c r="B61">
-        <v>1.1622483925269278</v>
+        <v>0.64452250739670258</v>
       </c>
       <c r="C61">
         <v>471.28397822006644</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-8.3671903606792632</v>
+        <v>-7.81797506719591</v>
       </c>
       <c r="B62">
-        <v>2.568169768088195</v>
+        <v>2.0449697135273834</v>
       </c>
       <c r="C62">
         <v>471.28397822006644</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-7.0304889727261877</v>
+        <v>-6.47666819145885</v>
       </c>
       <c r="B63">
-        <v>3.95954566138766</v>
+        <v>3.4323533726555011</v>
       </c>
       <c r="C63">
         <v>471.28397822006644</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-5.679743942537578</v>
+        <v>-5.1234424358492907</v>
       </c>
       <c r="B64">
-        <v>5.3381425675700669</v>
+        <v>4.8089440904389029</v>
       </c>
       <c r="C64">
         <v>471.28397822006644</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-4.317311158416933</v>
+        <v>-3.7613423948216571</v>
       </c>
       <c r="B65">
-        <v>6.7061042229806267</v>
+        <v>6.1774988482144577</v>
       </c>
       <c r="C65">
         <v>471.28397822006644</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.9455465086677322</v>
+        <v>-2.3934126628303596</v>
       </c>
       <c r="B66">
-        <v>8.06557436396456</v>
+        <v>7.5407746273190552</v>
       </c>
       <c r="C66">
         <v>471.28397822006644</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.563714331878953</v>
+        <v>-1.0187166289193343</v>
       </c>
       <c r="B67">
-        <v>9.4158835767375777</v>
+        <v>8.897923295443297</v>
       </c>
       <c r="C67">
         <v>471.28397822006644</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.15871276778151205</v>
+        <v>0.37960713950942537</v>
       </c>
       <c r="B68">
-        <v>10.745109846997401</v>
+        <v>10.23367626569269</v>
       </c>
       <c r="C68">
         <v>471.28397822006644</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.279634117607821</v>
+        <v>1.8146463895634635</v>
       </c>
       <c r="B69">
-        <v>12.043993601828763</v>
+        <v>11.536182148643281</v>
       </c>
       <c r="C69">
         <v>471.28397822006644</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.7374323542707817</v>
+        <v>3.2684693047465472</v>
       </c>
       <c r="B70">
-        <v>13.325177634382504</v>
+        <v>12.82167879933837</v>
       </c>
       <c r="C70">
         <v>471.28397822006644</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4.1995342714408341</v>
+        <v>4.7215258310602781</v>
       </c>
       <c r="B71">
-        <v>14.602445540561504</v>
+        <v>14.107869440593204</v>
       </c>
       <c r="C71">
         <v>471.28397822006644</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5.6698472993597777</v>
+        <v>6.1788125281013384</v>
       </c>
       <c r="B72">
-        <v>15.872241761210704</v>
+        <v>15.390229521843516</v>
       </c>
       <c r="C72">
         <v>471.28397822006644</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7.1548226104489521</v>
+        <v>7.6486003550787229</v>
       </c>
       <c r="B73">
-        <v>17.128696063531549</v>
+        <v>16.661269414989839</v>
       </c>
       <c r="C73">
         <v>471.28397822006644</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8.6520312448394456</v>
+        <v>9.12771125605557</v>
       </c>
       <c r="B74">
-        <v>18.374018675209427</v>
+        <v>17.923866955171363</v>
       </c>
       <c r="C74">
         <v>471.28397822006644</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>10.156781640877435</v>
+        <v>10.610048288323078</v>
       </c>
       <c r="B75">
-        <v>19.612478674374341</v>
+        <v>19.183543126385086</v>
       </c>
       <c r="C75">
         <v>471.28397822006644</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>11.664211962059689</v>
+        <v>12.0892879772305</v>
       </c>
       <c r="B76">
-        <v>20.848500080450719</v>
+        <v>20.446024044820646</v>
       </c>
       <c r="C76">
         <v>471.28397822006644</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>13.169848682350413</v>
+        <v>13.559603395021675</v>
       </c>
       <c r="B77">
-        <v>22.086153570448186</v>
+        <v>21.716586186972908</v>
       </c>
       <c r="C77">
         <v>471.28397822006644</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>14.670941792432922</v>
+        <v>15.017380333460608</v>
       </c>
       <c r="B78">
-        <v>23.3279415104225</v>
+        <v>22.998502338364993</v>
       </c>
       <c r="C78">
         <v>471.28397822006644</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>16.162647195332944</v>
+        <v>16.456302475785108</v>
       </c>
       <c r="B79">
-        <v>24.578271777745513</v>
+        <v>24.297492133480876</v>
       </c>
       <c r="C79">
         <v>471.28397822006644</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>17.636302582507472</v>
+        <v>17.865125689963534</v>
       </c>
       <c r="B80">
-        <v>25.845026624572213</v>
+        <v>25.623737507098667</v>
       </c>
       <c r="C80">
         <v>471.28397822006644</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>19.070249587076</v>
+        <v>19.215853430755743</v>
       </c>
       <c r="B81">
-        <v>27.147914043081617</v>
+        <v>27.002590260215118</v>
       </c>
       <c r="C81">
         <v>471.28397822006644</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>20.069389397282226</v>
+        <v>19.999288131866013</v>
       </c>
       <c r="B82">
-        <v>28.84645348988775</v>
+        <v>28.895145690768942</v>
       </c>
       <c r="C82">
         <v>471.28397822006644</v>
